--- a/06_放款/OCR全量需求范围测算.xlsx
+++ b/06_放款/OCR全量需求范围测算.xlsx
@@ -64,7 +64,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +121,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -504,7 +512,6 @@
           <t>口径：一份文件=分类+提取+规则整套；同一文件跨主体/跨阶段/同族版式折叠为 1。数据来源：客户承诺清单矩阵 + OCR_fields_CRA_414 字段清单。</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -608,15 +615,15 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>B1&amp;2 已交付（待与交付记录核对）</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>12</v>
+          <t>B1&amp;2 已交付（按客户提供清单核实）</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>21</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>按“主文件+收入+1 车辆文件”推定</t>
+          <t>22 项客户清单 → 折叠为 21 类</t>
         </is>
       </c>
     </row>
@@ -642,7 +649,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -698,7 +705,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>注：黄色底纹 = 需要业务确认的推定项（B1&amp;2 实际交付清单、SI Form 归属、纸签协议是否 OCR）。</t>
+          <t>注：绿色=B1&amp;2 已交付；黄色=待确认项（SPGA/SPOA-i 对应关系、EC/EPF 蓝色高亮含义、SG 驾照版式覆盖、SI Form 归属）。</t>
         </is>
       </c>
     </row>
@@ -781,404 +788,432 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>MyKad (Blue IC)</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>个人身份</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>申请+放款</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人/卖家/董事</t>
         </is>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>放款侧 NRIC/Director NRIC 为同引擎复用</t>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>放款侧 NRIC/Director NRIC 为同引擎复用；客户交付名: Mykad(Blue)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>MyPR (Red IC)</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>个人身份</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr"/>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>客户交付名: MyPR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Passport</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>个人身份</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>申请+放款</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>放款侧复用</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Malaysia Residence Pass (MEV)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>个人身份</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>外籍场景；客户交付名: VISA；客户清单名 VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Singapore Identity Card</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>个人身份</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>申请</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>申请人/担保人</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>SG 场景；客户交付名: SG_Identity_Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>SG Work Permit (含 MOM checking)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>个人身份</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>申请</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>申请人/担保人</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>2 变体折叠；客户交付名: SG_Work_Permit / _MOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Work Permit</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>个人身份</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>申请</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>申请人/担保人</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>客户交付名: work_Permit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Driving License (Malaysia)</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>个人身份</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>申请+放款</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>申请人/担保人</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>放款侧复用；客户交付名: Driving_Licence</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Driving License (SG)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>个人身份</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>申请</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>申请人/担保人</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>B3-补齐</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>外籍场景</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Singapore Identity Card</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>个人身份</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>申请</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>申请人/担保人</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>SG 场景</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>SG Work Permit (含 MOM checking)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>个人身份</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>申请</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>申请人/担保人</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>2 变体折叠</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Work Permit</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>个人身份</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>申请</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>申请人/担保人</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Driving License (Malaysia)</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>个人身份</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>申请+放款</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>申请人/担保人</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>B1&amp;2</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>放款侧复用</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Driving License (SG)</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>个人身份</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>申请</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>申请人/担保人</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>客户清单仅一项 Driving_Licence，是否已覆盖 SG 版式待确认</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -1565,350 +1600,378 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Form B</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Form BE</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="J21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>EA Form (PLC/MNC/GLC)</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>客户交付名: EA_Form</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>CP 58</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr"/>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>客户交付名: CP58</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>EC Form (GLC)</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr"/>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>客户交付名: EC_Form；客户清单蓝色高亮，含义待确认</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>NOA (Singapore Tax)</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>客户交付名: Singapore_Notice_of_Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Salary Slip (PLC/MNC/GLC)</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr"/>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>客户交付名: Payslip</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Bank Statement (Individual)</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>申请+放款</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人/卖家</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>放款侧 Seller Bank Statement 同引擎</t>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>放款侧 Seller Bank Statement 同引擎；客户交付名: Individual_bank_statement</t>
         </is>
       </c>
     </row>
@@ -1946,7 +2009,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>已交付(待核对)</t>
+          <t>已交付(B1&amp;2)</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -1954,7 +2017,11 @@
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>客户交付名: EPF_Statement；客户清单蓝色高亮，含义待确认</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
@@ -2037,174 +2104,194 @@
       <c r="J30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>PTPTN Letter</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr"/>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>客户交付名: PTPTN_Statement</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>SPOA-i Report</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>申请人/担保人</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr"/>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>客户交付名: SPGA；客户清单名 SPGA，同一文件待确认</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Consent CRA Form</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>申请-其他</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>申请人/担保人/卖家</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr"/>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>B3-补齐</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>无 e-consent 时强制</t>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>无 e-consent 时强制；客户交付名: CRA Form</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Vehicle Sales Order</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>申请-车辆</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>申请</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>申请人</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>已交付(待核对)</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>已交付(B1&amp;2)</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>B1&amp;2</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>B1&amp;2 的那份车辆文件(待核对)</t>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>B1&amp;2 的那份车辆文件(待核对)；客户交付名: VSO</t>
         </is>
       </c>
     </row>
